--- a/Paradigms/P0000_SpoutAssoc.xlsx
+++ b/Paradigms/P0000_SpoutAssoc.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="436">
   <si>
     <t>Object Definition</t>
   </si>
@@ -110,10 +110,13 @@
     <t>Deathzone Action</t>
   </si>
   <si>
+    <t>teleportation</t>
+  </si>
+  <si>
     <t>slow down</t>
   </si>
   <si>
-    <t>teleportation</t>
+    <t/>
   </si>
   <si>
     <t>x0</t>
@@ -1410,7 +1413,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1455,6 +1458,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="5" applyFill="1" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -1777,824 +1783,824 @@
   <dimension ref="A1:GU249"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="17" width="4.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="17" width="2.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="17" width="2.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="17" width="2.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="17" width="2.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="17" width="2.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="17" width="2.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="17" width="2.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="17" width="2.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="17" width="2.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="17" width="3.7192857142857143" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="27" max="27" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="28" max="28" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="29" max="29" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="30" max="30" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="31" max="31" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="32" max="32" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="33" max="33" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="34" max="34" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="35" max="35" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="36" max="36" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="37" max="37" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="38" max="38" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="39" max="39" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="40" max="40" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="41" max="41" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="42" max="42" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="43" max="43" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="44" max="44" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="45" max="45" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="46" max="46" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="47" max="47" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="48" max="48" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="49" max="49" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="50" max="50" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="51" max="51" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="52" max="52" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="53" max="53" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="54" max="54" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="55" max="55" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="56" max="56" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="57" max="57" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="58" max="58" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="59" max="59" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="60" max="60" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="61" max="61" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="62" max="62" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="63" max="63" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="64" max="64" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="65" max="65" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="66" max="66" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="67" max="67" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="68" max="68" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="69" max="69" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="70" max="70" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="71" max="71" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="72" max="72" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="73" max="73" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="74" max="74" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="75" max="75" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="76" max="76" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="77" max="77" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="78" max="78" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="79" max="79" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="80" max="80" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="81" max="81" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="82" max="82" style="16" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="83" max="83" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="84" max="84" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="85" max="85" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="86" max="86" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="87" max="87" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="88" max="88" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="89" max="89" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="90" max="90" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="91" max="91" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="92" max="92" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="93" max="93" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="94" max="94" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="95" max="95" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="96" max="96" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="97" max="97" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="98" max="98" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="99" max="99" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="100" max="100" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="101" max="101" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="102" max="102" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="103" max="103" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="104" max="104" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="105" max="105" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="106" max="106" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="107" max="107" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="108" max="108" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="109" max="109" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="110" max="110" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="111" max="111" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="112" max="112" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="113" max="113" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="114" max="114" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="115" max="115" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="116" max="116" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="117" max="117" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="118" max="118" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="119" max="119" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="120" max="120" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="121" max="121" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="122" max="122" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="123" max="123" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="124" max="124" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="125" max="125" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="126" max="126" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="127" max="127" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="128" max="128" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="129" max="129" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="130" max="130" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="131" max="131" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="132" max="132" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="133" max="133" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="134" max="134" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="135" max="135" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="136" max="136" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="137" max="137" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="138" max="138" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="139" max="139" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="140" max="140" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="141" max="141" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="142" max="142" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="143" max="143" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="144" max="144" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="145" max="145" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="146" max="146" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="147" max="147" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="148" max="148" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="149" max="149" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="150" max="150" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="151" max="151" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="152" max="152" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="153" max="153" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="154" max="154" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="155" max="155" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="156" max="156" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="157" max="157" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="158" max="158" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="159" max="159" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="160" max="160" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="161" max="161" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="162" max="162" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="163" max="163" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="164" max="164" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="165" max="165" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="166" max="166" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="167" max="167" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="168" max="168" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="169" max="169" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="170" max="170" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="171" max="171" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="172" max="172" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="173" max="173" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="174" max="174" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="175" max="175" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="176" max="176" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="177" max="177" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="178" max="178" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="179" max="179" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="180" max="180" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="181" max="181" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="182" max="182" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="183" max="183" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="184" max="184" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="185" max="185" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="186" max="186" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="187" max="187" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="188" max="188" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="189" max="189" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="190" max="190" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="191" max="191" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="192" max="192" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="193" max="193" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="194" max="194" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="195" max="195" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="196" max="196" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="197" max="197" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="198" max="198" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="199" max="199" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="200" max="200" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="201" max="201" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="202" max="202" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="203" max="203" style="17" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="18" width="4.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="18" width="2.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="18" width="2.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="18" width="2.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="18" width="2.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="18" width="2.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="18" width="2.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="18" width="2.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="18" width="2.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="18" width="2.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="18" width="3.7192857142857143" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="27" max="27" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="28" max="28" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="29" max="29" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="30" max="30" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="31" max="31" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="32" max="32" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="33" max="33" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="34" max="34" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="35" max="35" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="36" max="36" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="37" max="37" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="38" max="38" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="39" max="39" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="40" max="40" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="41" max="41" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="42" max="42" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="43" max="43" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="44" max="44" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="45" max="45" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="46" max="46" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="47" max="47" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="48" max="48" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="49" max="49" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="50" max="50" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="51" max="51" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="52" max="52" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="53" max="53" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="54" max="54" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="55" max="55" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="56" max="56" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="57" max="57" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="58" max="58" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="59" max="59" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="60" max="60" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="61" max="61" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="62" max="62" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="63" max="63" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="64" max="64" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="65" max="65" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="66" max="66" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="67" max="67" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="68" max="68" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="69" max="69" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="70" max="70" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="71" max="71" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="72" max="72" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="73" max="73" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="74" max="74" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="75" max="75" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="76" max="76" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="77" max="77" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="78" max="78" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="79" max="79" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="80" max="80" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="81" max="81" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="82" max="82" style="17" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="83" max="83" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="84" max="84" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="85" max="85" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="86" max="86" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="87" max="87" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="88" max="88" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="89" max="89" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="90" max="90" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="91" max="91" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="92" max="92" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="93" max="93" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="94" max="94" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="95" max="95" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="96" max="96" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="97" max="97" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="98" max="98" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="99" max="99" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="100" max="100" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="101" max="101" style="18" width="3.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="102" max="102" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="103" max="103" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="104" max="104" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="105" max="105" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="106" max="106" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="107" max="107" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="108" max="108" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="109" max="109" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="110" max="110" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="111" max="111" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="112" max="112" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="113" max="113" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="114" max="114" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="115" max="115" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="116" max="116" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="117" max="117" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="118" max="118" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="119" max="119" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="120" max="120" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="121" max="121" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="122" max="122" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="123" max="123" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="124" max="124" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="125" max="125" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="126" max="126" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="127" max="127" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="128" max="128" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="129" max="129" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="130" max="130" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="131" max="131" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="132" max="132" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="133" max="133" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="134" max="134" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="135" max="135" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="136" max="136" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="137" max="137" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="138" max="138" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="139" max="139" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="140" max="140" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="141" max="141" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="142" max="142" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="143" max="143" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="144" max="144" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="145" max="145" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="146" max="146" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="147" max="147" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="148" max="148" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="149" max="149" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="150" max="150" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="151" max="151" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="152" max="152" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="153" max="153" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="154" max="154" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="155" max="155" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="156" max="156" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="157" max="157" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="158" max="158" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="159" max="159" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="160" max="160" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="161" max="161" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="162" max="162" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="163" max="163" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="164" max="164" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="165" max="165" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="166" max="166" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="167" max="167" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="168" max="168" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="169" max="169" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="170" max="170" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="171" max="171" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="172" max="172" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="173" max="173" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="174" max="174" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="175" max="175" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="176" max="176" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="177" max="177" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="178" max="178" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="179" max="179" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="180" max="180" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="181" max="181" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="182" max="182" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="183" max="183" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="184" max="184" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="185" max="185" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="186" max="186" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="187" max="187" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="188" max="188" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="189" max="189" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="190" max="190" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="191" max="191" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="192" max="192" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="193" max="193" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="194" max="194" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="195" max="195" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="196" max="196" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="197" max="197" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="198" max="198" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="199" max="199" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="200" max="200" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="201" max="201" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="202" max="202" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="203" max="203" style="18" width="5.862142857142857" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
-      <c r="A1" s="18"/>
+      <c r="A1" s="19"/>
       <c r="B1" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C1" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="C1" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="D1" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="E1" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="F1" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="G1" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="H1" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="I1" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="J1" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="L1" s="18" t="s">
+      <c r="K1" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="L1" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="M1" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="O1" s="18" t="s">
+      <c r="N1" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="P1" s="18" t="s">
+      <c r="O1" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="Q1" s="18" t="s">
+      <c r="P1" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="R1" s="18" t="s">
+      <c r="Q1" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="S1" s="18" t="s">
+      <c r="R1" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="T1" s="18" t="s">
+      <c r="S1" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="U1" s="18" t="s">
+      <c r="T1" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="V1" s="18" t="s">
+      <c r="U1" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="W1" s="18" t="s">
+      <c r="V1" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="X1" s="18" t="s">
+      <c r="W1" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="Y1" s="18" t="s">
+      <c r="X1" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="Z1" s="18" t="s">
+      <c r="Y1" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="AA1" s="18" t="s">
+      <c r="Z1" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="AB1" s="18" t="s">
+      <c r="AA1" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="AC1" s="18" t="s">
+      <c r="AB1" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="AD1" s="18" t="s">
+      <c r="AC1" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="AE1" s="18" t="s">
+      <c r="AD1" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="AF1" s="18" t="s">
+      <c r="AE1" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="AG1" s="18" t="s">
+      <c r="AF1" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="AH1" s="18" t="s">
+      <c r="AG1" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="AI1" s="18" t="s">
+      <c r="AH1" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="AJ1" s="18" t="s">
+      <c r="AI1" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="AK1" s="18" t="s">
+      <c r="AJ1" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="AL1" s="18" t="s">
+      <c r="AK1" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="AM1" s="18" t="s">
+      <c r="AL1" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="AN1" s="18" t="s">
+      <c r="AM1" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="AO1" s="18" t="s">
+      <c r="AN1" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="AP1" s="18" t="s">
+      <c r="AO1" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="AQ1" s="18" t="s">
+      <c r="AP1" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="AR1" s="18" t="s">
+      <c r="AQ1" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="AS1" s="18" t="s">
+      <c r="AR1" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="AT1" s="18" t="s">
+      <c r="AS1" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="AU1" s="18" t="s">
+      <c r="AT1" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="AV1" s="18" t="s">
+      <c r="AU1" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="AW1" s="18" t="s">
+      <c r="AV1" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="AX1" s="18" t="s">
+      <c r="AW1" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="AY1" s="18" t="s">
+      <c r="AX1" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="AZ1" s="18" t="s">
+      <c r="AY1" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="BA1" s="18" t="s">
+      <c r="AZ1" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="BB1" s="18" t="s">
+      <c r="BA1" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="BC1" s="18" t="s">
+      <c r="BB1" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="BD1" s="18" t="s">
+      <c r="BC1" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="BE1" s="18" t="s">
+      <c r="BD1" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="BF1" s="18" t="s">
+      <c r="BE1" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="BG1" s="18" t="s">
+      <c r="BF1" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="BH1" s="18" t="s">
+      <c r="BG1" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="BI1" s="18" t="s">
+      <c r="BH1" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="BJ1" s="18" t="s">
+      <c r="BI1" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="BK1" s="18" t="s">
+      <c r="BJ1" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="BL1" s="18" t="s">
+      <c r="BK1" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="BM1" s="18" t="s">
+      <c r="BL1" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="BN1" s="18" t="s">
+      <c r="BM1" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="BO1" s="18" t="s">
+      <c r="BN1" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="BP1" s="18" t="s">
+      <c r="BO1" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="BQ1" s="18" t="s">
+      <c r="BP1" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="BR1" s="18" t="s">
+      <c r="BQ1" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="BS1" s="18" t="s">
+      <c r="BR1" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="BT1" s="18" t="s">
+      <c r="BS1" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="BU1" s="18" t="s">
+      <c r="BT1" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="BV1" s="18" t="s">
+      <c r="BU1" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="BW1" s="18" t="s">
+      <c r="BV1" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="BX1" s="18" t="s">
+      <c r="BW1" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="BY1" s="18" t="s">
+      <c r="BX1" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="BZ1" s="18" t="s">
+      <c r="BY1" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="CA1" s="18" t="s">
+      <c r="BZ1" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="CB1" s="18" t="s">
+      <c r="CA1" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="CC1" s="18" t="s">
+      <c r="CB1" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="CD1" s="19" t="s">
+      <c r="CC1" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="CE1" s="18" t="s">
+      <c r="CD1" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="CF1" s="18" t="s">
+      <c r="CE1" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="CG1" s="18" t="s">
+      <c r="CF1" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="CH1" s="18" t="s">
+      <c r="CG1" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="CI1" s="18" t="s">
+      <c r="CH1" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="CJ1" s="18" t="s">
+      <c r="CI1" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="CK1" s="18" t="s">
+      <c r="CJ1" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="CL1" s="18" t="s">
+      <c r="CK1" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="CM1" s="18" t="s">
+      <c r="CL1" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="CN1" s="18" t="s">
+      <c r="CM1" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="CO1" s="18" t="s">
+      <c r="CN1" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="CP1" s="18" t="s">
+      <c r="CO1" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="CQ1" s="18" t="s">
+      <c r="CP1" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="CR1" s="18" t="s">
+      <c r="CQ1" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="CS1" s="18" t="s">
+      <c r="CR1" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="CT1" s="18" t="s">
+      <c r="CS1" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="CU1" s="18" t="s">
+      <c r="CT1" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="CV1" s="18" t="s">
+      <c r="CU1" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="CW1" s="18" t="s">
+      <c r="CV1" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="CX1" s="18" t="s">
+      <c r="CW1" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="CY1" s="18" t="s">
+      <c r="CX1" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="CZ1" s="18" t="s">
+      <c r="CY1" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="DA1" s="18" t="s">
+      <c r="CZ1" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="DB1" s="18" t="s">
+      <c r="DA1" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="DC1" s="18" t="s">
+      <c r="DB1" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="DD1" s="18" t="s">
+      <c r="DC1" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="DE1" s="18" t="s">
+      <c r="DD1" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="DF1" s="18" t="s">
+      <c r="DE1" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="DG1" s="18" t="s">
+      <c r="DF1" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="DH1" s="18" t="s">
+      <c r="DG1" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="DI1" s="18" t="s">
+      <c r="DH1" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="DJ1" s="18" t="s">
+      <c r="DI1" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="DK1" s="18" t="s">
+      <c r="DJ1" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="DL1" s="18" t="s">
+      <c r="DK1" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="DM1" s="18" t="s">
+      <c r="DL1" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="DN1" s="18" t="s">
+      <c r="DM1" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="DO1" s="18" t="s">
+      <c r="DN1" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="DP1" s="18" t="s">
+      <c r="DO1" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="DQ1" s="18" t="s">
+      <c r="DP1" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="DR1" s="18" t="s">
+      <c r="DQ1" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="DS1" s="18" t="s">
+      <c r="DR1" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="DT1" s="18" t="s">
+      <c r="DS1" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="DU1" s="18" t="s">
+      <c r="DT1" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="DV1" s="18" t="s">
+      <c r="DU1" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="DW1" s="18" t="s">
+      <c r="DV1" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="DX1" s="18" t="s">
+      <c r="DW1" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="DY1" s="18" t="s">
+      <c r="DX1" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="DZ1" s="18" t="s">
+      <c r="DY1" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="EA1" s="18" t="s">
+      <c r="DZ1" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="EB1" s="18" t="s">
+      <c r="EA1" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="EC1" s="18" t="s">
+      <c r="EB1" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="ED1" s="18" t="s">
+      <c r="EC1" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="EE1" s="18" t="s">
+      <c r="ED1" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="EF1" s="18" t="s">
+      <c r="EE1" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="EG1" s="18" t="s">
+      <c r="EF1" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="EH1" s="18" t="s">
+      <c r="EG1" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="EI1" s="18" t="s">
+      <c r="EH1" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="EJ1" s="18" t="s">
+      <c r="EI1" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="EK1" s="18" t="s">
+      <c r="EJ1" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="EL1" s="18" t="s">
+      <c r="EK1" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="EM1" s="18" t="s">
+      <c r="EL1" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="EN1" s="18" t="s">
+      <c r="EM1" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="EO1" s="18" t="s">
+      <c r="EN1" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="EP1" s="18" t="s">
+      <c r="EO1" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="EQ1" s="18" t="s">
+      <c r="EP1" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="ER1" s="18" t="s">
+      <c r="EQ1" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="ES1" s="18" t="s">
+      <c r="ER1" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="ET1" s="18" t="s">
+      <c r="ES1" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="EU1" s="18" t="s">
+      <c r="ET1" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="EV1" s="18" t="s">
+      <c r="EU1" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="EW1" s="18" t="s">
+      <c r="EV1" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="EX1" s="18" t="s">
+      <c r="EW1" s="19" t="s">
         <v>185</v>
       </c>
-      <c r="EY1" s="18" t="s">
+      <c r="EX1" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="EZ1" s="18" t="s">
+      <c r="EY1" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="FA1" s="18" t="s">
+      <c r="EZ1" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="FB1" s="18" t="s">
+      <c r="FA1" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="FC1" s="18" t="s">
+      <c r="FB1" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="FD1" s="18" t="s">
+      <c r="FC1" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="FE1" s="18" t="s">
+      <c r="FD1" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="FF1" s="18" t="s">
+      <c r="FE1" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="FG1" s="18" t="s">
+      <c r="FF1" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="FH1" s="18" t="s">
+      <c r="FG1" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="FI1" s="18" t="s">
+      <c r="FH1" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="FJ1" s="18" t="s">
+      <c r="FI1" s="19" t="s">
         <v>197</v>
       </c>
-      <c r="FK1" s="18" t="s">
+      <c r="FJ1" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="FL1" s="18" t="s">
+      <c r="FK1" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="FM1" s="18" t="s">
+      <c r="FL1" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="FN1" s="18" t="s">
+      <c r="FM1" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="FO1" s="18" t="s">
+      <c r="FN1" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="FP1" s="18" t="s">
+      <c r="FO1" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="FQ1" s="18" t="s">
+      <c r="FP1" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="FR1" s="18" t="s">
+      <c r="FQ1" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="FS1" s="18" t="s">
+      <c r="FR1" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="FT1" s="18" t="s">
+      <c r="FS1" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="FU1" s="18" t="s">
+      <c r="FT1" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="FV1" s="18" t="s">
+      <c r="FU1" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="FW1" s="18" t="s">
+      <c r="FV1" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="FX1" s="18" t="s">
+      <c r="FW1" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="FY1" s="18" t="s">
+      <c r="FX1" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="FZ1" s="18" t="s">
+      <c r="FY1" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="GA1" s="18" t="s">
+      <c r="FZ1" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="GB1" s="18" t="s">
+      <c r="GA1" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="GC1" s="18" t="s">
+      <c r="GB1" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="GD1" s="18" t="s">
+      <c r="GC1" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="GE1" s="18" t="s">
+      <c r="GD1" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="GF1" s="18" t="s">
+      <c r="GE1" s="19" t="s">
         <v>219</v>
       </c>
-      <c r="GG1" s="18" t="s">
+      <c r="GF1" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="GH1" s="18" t="s">
+      <c r="GG1" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="GI1" s="18" t="s">
+      <c r="GH1" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="GJ1" s="18" t="s">
+      <c r="GI1" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="GK1" s="18" t="s">
+      <c r="GJ1" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="GL1" s="18" t="s">
+      <c r="GK1" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="GM1" s="18" t="s">
+      <c r="GL1" s="19" t="s">
         <v>226</v>
       </c>
-      <c r="GN1" s="18" t="s">
+      <c r="GM1" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="GO1" s="18" t="s">
+      <c r="GN1" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="GP1" s="18" t="s">
+      <c r="GO1" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="GQ1" s="18" t="s">
+      <c r="GP1" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="GR1" s="18" t="s">
+      <c r="GQ1" s="19" t="s">
         <v>231</v>
       </c>
-      <c r="GS1" s="18" t="s">
+      <c r="GR1" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="GT1" s="18" t="s">
+      <c r="GS1" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="GU1" s="18"/>
+      <c r="GT1" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="GU1" s="19"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
@@ -2797,11 +2803,11 @@
       <c r="GU2" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
-      <c r="A3" s="18" t="s">
-        <v>235</v>
+      <c r="A3" s="19" t="s">
+        <v>236</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -3004,8 +3010,8 @@
       <c r="GU3" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="18" t="s">
-        <v>236</v>
+      <c r="A4" s="19" t="s">
+        <v>237</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -3211,8 +3217,8 @@
       <c r="GU4" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
-      <c r="A5" s="18" t="s">
-        <v>237</v>
+      <c r="A5" s="19" t="s">
+        <v>238</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -3418,8 +3424,8 @@
       <c r="GU5" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="18" t="s">
-        <v>238</v>
+      <c r="A6" s="19" t="s">
+        <v>239</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -3625,8 +3631,8 @@
       <c r="GU6" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
-      <c r="A7" s="18" t="s">
-        <v>239</v>
+      <c r="A7" s="19" t="s">
+        <v>240</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -3832,8 +3838,8 @@
       <c r="GU7" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
-      <c r="A8" s="18" t="s">
-        <v>240</v>
+      <c r="A8" s="19" t="s">
+        <v>241</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -4039,8 +4045,8 @@
       <c r="GU8" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
-      <c r="A9" s="18" t="s">
-        <v>241</v>
+      <c r="A9" s="19" t="s">
+        <v>242</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -4246,8 +4252,8 @@
       <c r="GU9" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
-      <c r="A10" s="18" t="s">
-        <v>242</v>
+      <c r="A10" s="19" t="s">
+        <v>243</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -4453,8 +4459,8 @@
       <c r="GU10" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
-      <c r="A11" s="18" t="s">
-        <v>243</v>
+      <c r="A11" s="19" t="s">
+        <v>244</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -4660,8 +4666,8 @@
       <c r="GU11" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
-      <c r="A12" s="18" t="s">
-        <v>244</v>
+      <c r="A12" s="19" t="s">
+        <v>245</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -4867,8 +4873,8 @@
       <c r="GU12" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
-      <c r="A13" s="18" t="s">
-        <v>245</v>
+      <c r="A13" s="19" t="s">
+        <v>246</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -5074,8 +5080,8 @@
       <c r="GU13" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
-      <c r="A14" s="18" t="s">
-        <v>246</v>
+      <c r="A14" s="19" t="s">
+        <v>247</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -5281,8 +5287,8 @@
       <c r="GU14" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
-      <c r="A15" s="18" t="s">
-        <v>247</v>
+      <c r="A15" s="19" t="s">
+        <v>248</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -5488,8 +5494,8 @@
       <c r="GU15" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
-      <c r="A16" s="18" t="s">
-        <v>248</v>
+      <c r="A16" s="19" t="s">
+        <v>249</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -5695,8 +5701,8 @@
       <c r="GU16" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
-      <c r="A17" s="18" t="s">
-        <v>249</v>
+      <c r="A17" s="19" t="s">
+        <v>250</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -5902,8 +5908,8 @@
       <c r="GU17" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
-      <c r="A18" s="18" t="s">
-        <v>250</v>
+      <c r="A18" s="19" t="s">
+        <v>251</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -6109,8 +6115,8 @@
       <c r="GU18" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
-      <c r="A19" s="18" t="s">
-        <v>251</v>
+      <c r="A19" s="19" t="s">
+        <v>252</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -6316,8 +6322,8 @@
       <c r="GU19" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
-      <c r="A20" s="18" t="s">
-        <v>252</v>
+      <c r="A20" s="19" t="s">
+        <v>253</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -6523,8 +6529,8 @@
       <c r="GU20" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
-      <c r="A21" s="18" t="s">
-        <v>253</v>
+      <c r="A21" s="19" t="s">
+        <v>254</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -6730,8 +6736,8 @@
       <c r="GU21" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
-      <c r="A22" s="18" t="s">
-        <v>254</v>
+      <c r="A22" s="19" t="s">
+        <v>255</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -6937,8 +6943,8 @@
       <c r="GU22" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
-      <c r="A23" s="18" t="s">
-        <v>255</v>
+      <c r="A23" s="19" t="s">
+        <v>256</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -7144,8 +7150,8 @@
       <c r="GU23" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
-      <c r="A24" s="18" t="s">
-        <v>256</v>
+      <c r="A24" s="19" t="s">
+        <v>257</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -7351,8 +7357,8 @@
       <c r="GU24" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
-      <c r="A25" s="18" t="s">
-        <v>257</v>
+      <c r="A25" s="19" t="s">
+        <v>258</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -7558,8 +7564,8 @@
       <c r="GU25" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
-      <c r="A26" s="18" t="s">
-        <v>258</v>
+      <c r="A26" s="19" t="s">
+        <v>259</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -7765,8 +7771,8 @@
       <c r="GU26" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
-      <c r="A27" s="18" t="s">
-        <v>259</v>
+      <c r="A27" s="19" t="s">
+        <v>260</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -7972,8 +7978,8 @@
       <c r="GU27" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
-      <c r="A28" s="18" t="s">
-        <v>260</v>
+      <c r="A28" s="19" t="s">
+        <v>261</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -8179,8 +8185,8 @@
       <c r="GU28" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
-      <c r="A29" s="18" t="s">
-        <v>261</v>
+      <c r="A29" s="19" t="s">
+        <v>262</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -8386,8 +8392,8 @@
       <c r="GU29" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
-      <c r="A30" s="18" t="s">
-        <v>262</v>
+      <c r="A30" s="19" t="s">
+        <v>263</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -8593,8 +8599,8 @@
       <c r="GU30" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
-      <c r="A31" s="18" t="s">
-        <v>263</v>
+      <c r="A31" s="19" t="s">
+        <v>264</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -8800,8 +8806,8 @@
       <c r="GU31" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
-      <c r="A32" s="18" t="s">
-        <v>264</v>
+      <c r="A32" s="19" t="s">
+        <v>265</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -9007,8 +9013,8 @@
       <c r="GU32" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
-      <c r="A33" s="18" t="s">
-        <v>265</v>
+      <c r="A33" s="19" t="s">
+        <v>266</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -9214,8 +9220,8 @@
       <c r="GU33" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
-      <c r="A34" s="18" t="s">
-        <v>266</v>
+      <c r="A34" s="19" t="s">
+        <v>267</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -9421,8 +9427,8 @@
       <c r="GU34" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
-      <c r="A35" s="18" t="s">
-        <v>267</v>
+      <c r="A35" s="19" t="s">
+        <v>268</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -9628,8 +9634,8 @@
       <c r="GU35" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
-      <c r="A36" s="18" t="s">
-        <v>268</v>
+      <c r="A36" s="19" t="s">
+        <v>269</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -9835,8 +9841,8 @@
       <c r="GU36" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
-      <c r="A37" s="18" t="s">
-        <v>269</v>
+      <c r="A37" s="19" t="s">
+        <v>270</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -10042,8 +10048,8 @@
       <c r="GU37" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
-      <c r="A38" s="18" t="s">
-        <v>270</v>
+      <c r="A38" s="19" t="s">
+        <v>271</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -10249,8 +10255,8 @@
       <c r="GU38" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
-      <c r="A39" s="18" t="s">
-        <v>271</v>
+      <c r="A39" s="19" t="s">
+        <v>272</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -10456,8 +10462,8 @@
       <c r="GU39" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
-      <c r="A40" s="18" t="s">
-        <v>272</v>
+      <c r="A40" s="19" t="s">
+        <v>273</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -10663,8 +10669,8 @@
       <c r="GU40" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
-      <c r="A41" s="18" t="s">
-        <v>273</v>
+      <c r="A41" s="19" t="s">
+        <v>274</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -10870,8 +10876,8 @@
       <c r="GU41" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
-      <c r="A42" s="18" t="s">
-        <v>274</v>
+      <c r="A42" s="19" t="s">
+        <v>275</v>
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -11077,8 +11083,8 @@
       <c r="GU42" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
-      <c r="A43" s="18" t="s">
-        <v>275</v>
+      <c r="A43" s="19" t="s">
+        <v>276</v>
       </c>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -11284,8 +11290,8 @@
       <c r="GU43" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="19.5">
-      <c r="A44" s="18" t="s">
-        <v>276</v>
+      <c r="A44" s="19" t="s">
+        <v>277</v>
       </c>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -11491,8 +11497,8 @@
       <c r="GU44" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="19.5">
-      <c r="A45" s="18" t="s">
-        <v>277</v>
+      <c r="A45" s="19" t="s">
+        <v>278</v>
       </c>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -11698,8 +11704,8 @@
       <c r="GU45" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5">
-      <c r="A46" s="18" t="s">
-        <v>278</v>
+      <c r="A46" s="19" t="s">
+        <v>279</v>
       </c>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -11905,8 +11911,8 @@
       <c r="GU46" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="19.5">
-      <c r="A47" s="18" t="s">
-        <v>279</v>
+      <c r="A47" s="19" t="s">
+        <v>280</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -12112,8 +12118,8 @@
       <c r="GU47" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="19.5">
-      <c r="A48" s="18" t="s">
-        <v>280</v>
+      <c r="A48" s="19" t="s">
+        <v>281</v>
       </c>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -12319,8 +12325,8 @@
       <c r="GU48" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="19.5">
-      <c r="A49" s="18" t="s">
-        <v>281</v>
+      <c r="A49" s="19" t="s">
+        <v>282</v>
       </c>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -12526,8 +12532,8 @@
       <c r="GU49" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="19.5">
-      <c r="A50" s="18" t="s">
-        <v>282</v>
+      <c r="A50" s="19" t="s">
+        <v>283</v>
       </c>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -12733,8 +12739,8 @@
       <c r="GU50" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="19.5">
-      <c r="A51" s="18" t="s">
-        <v>283</v>
+      <c r="A51" s="19" t="s">
+        <v>284</v>
       </c>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -12940,8 +12946,8 @@
       <c r="GU51" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="19.5">
-      <c r="A52" s="18" t="s">
-        <v>284</v>
+      <c r="A52" s="19" t="s">
+        <v>285</v>
       </c>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -13147,8 +13153,8 @@
       <c r="GU52" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="19.5">
-      <c r="A53" s="18" t="s">
-        <v>285</v>
+      <c r="A53" s="19" t="s">
+        <v>286</v>
       </c>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -13354,8 +13360,8 @@
       <c r="GU53" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="19.5">
-      <c r="A54" s="18" t="s">
-        <v>286</v>
+      <c r="A54" s="19" t="s">
+        <v>287</v>
       </c>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -13561,8 +13567,8 @@
       <c r="GU54" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="19.5">
-      <c r="A55" s="18" t="s">
-        <v>287</v>
+      <c r="A55" s="19" t="s">
+        <v>288</v>
       </c>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -13768,8 +13774,8 @@
       <c r="GU55" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="19.5">
-      <c r="A56" s="18" t="s">
-        <v>288</v>
+      <c r="A56" s="19" t="s">
+        <v>289</v>
       </c>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -13975,8 +13981,8 @@
       <c r="GU56" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="19.5">
-      <c r="A57" s="18" t="s">
-        <v>289</v>
+      <c r="A57" s="19" t="s">
+        <v>290</v>
       </c>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -14182,8 +14188,8 @@
       <c r="GU57" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="19.5">
-      <c r="A58" s="18" t="s">
-        <v>290</v>
+      <c r="A58" s="19" t="s">
+        <v>291</v>
       </c>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -14389,8 +14395,8 @@
       <c r="GU58" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="19.5">
-      <c r="A59" s="18" t="s">
-        <v>291</v>
+      <c r="A59" s="19" t="s">
+        <v>292</v>
       </c>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -14596,8 +14602,8 @@
       <c r="GU59" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="19.5">
-      <c r="A60" s="18" t="s">
-        <v>292</v>
+      <c r="A60" s="19" t="s">
+        <v>293</v>
       </c>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -14803,8 +14809,8 @@
       <c r="GU60" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="19.5">
-      <c r="A61" s="18" t="s">
-        <v>293</v>
+      <c r="A61" s="19" t="s">
+        <v>294</v>
       </c>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -15010,8 +15016,8 @@
       <c r="GU61" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="19.5">
-      <c r="A62" s="18" t="s">
-        <v>294</v>
+      <c r="A62" s="19" t="s">
+        <v>295</v>
       </c>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -15217,8 +15223,8 @@
       <c r="GU62" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="19.5">
-      <c r="A63" s="18" t="s">
-        <v>295</v>
+      <c r="A63" s="19" t="s">
+        <v>296</v>
       </c>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -15424,8 +15430,8 @@
       <c r="GU63" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="19.5">
-      <c r="A64" s="18" t="s">
-        <v>296</v>
+      <c r="A64" s="19" t="s">
+        <v>297</v>
       </c>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -15631,8 +15637,8 @@
       <c r="GU64" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="19.5">
-      <c r="A65" s="18" t="s">
-        <v>297</v>
+      <c r="A65" s="19" t="s">
+        <v>298</v>
       </c>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -15838,8 +15844,8 @@
       <c r="GU65" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="19.5">
-      <c r="A66" s="18" t="s">
-        <v>298</v>
+      <c r="A66" s="19" t="s">
+        <v>299</v>
       </c>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -16045,8 +16051,8 @@
       <c r="GU66" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="19.5">
-      <c r="A67" s="18" t="s">
-        <v>299</v>
+      <c r="A67" s="19" t="s">
+        <v>300</v>
       </c>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -16252,8 +16258,8 @@
       <c r="GU67" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="19.5">
-      <c r="A68" s="18" t="s">
-        <v>300</v>
+      <c r="A68" s="19" t="s">
+        <v>301</v>
       </c>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -16459,8 +16465,8 @@
       <c r="GU68" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="19.5">
-      <c r="A69" s="18" t="s">
-        <v>301</v>
+      <c r="A69" s="19" t="s">
+        <v>302</v>
       </c>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -16666,8 +16672,8 @@
       <c r="GU69" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="19.5">
-      <c r="A70" s="18" t="s">
-        <v>302</v>
+      <c r="A70" s="19" t="s">
+        <v>303</v>
       </c>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -16873,8 +16879,8 @@
       <c r="GU70" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="19.5">
-      <c r="A71" s="18" t="s">
-        <v>303</v>
+      <c r="A71" s="19" t="s">
+        <v>304</v>
       </c>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -17080,8 +17086,8 @@
       <c r="GU71" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="19.5">
-      <c r="A72" s="18" t="s">
-        <v>304</v>
+      <c r="A72" s="19" t="s">
+        <v>305</v>
       </c>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -17287,8 +17293,8 @@
       <c r="GU72" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="19.5">
-      <c r="A73" s="18" t="s">
-        <v>305</v>
+      <c r="A73" s="19" t="s">
+        <v>306</v>
       </c>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -17494,8 +17500,8 @@
       <c r="GU73" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="19.5">
-      <c r="A74" s="18" t="s">
-        <v>306</v>
+      <c r="A74" s="19" t="s">
+        <v>307</v>
       </c>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -17701,8 +17707,8 @@
       <c r="GU74" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="19.5">
-      <c r="A75" s="18" t="s">
-        <v>307</v>
+      <c r="A75" s="19" t="s">
+        <v>308</v>
       </c>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -17908,8 +17914,8 @@
       <c r="GU75" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="19.5">
-      <c r="A76" s="18" t="s">
-        <v>308</v>
+      <c r="A76" s="19" t="s">
+        <v>309</v>
       </c>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -18115,8 +18121,8 @@
       <c r="GU76" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="19.5">
-      <c r="A77" s="18" t="s">
-        <v>309</v>
+      <c r="A77" s="19" t="s">
+        <v>310</v>
       </c>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -18322,8 +18328,8 @@
       <c r="GU77" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="19.5">
-      <c r="A78" s="18" t="s">
-        <v>310</v>
+      <c r="A78" s="19" t="s">
+        <v>311</v>
       </c>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -18529,8 +18535,8 @@
       <c r="GU78" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="19.5">
-      <c r="A79" s="18" t="s">
-        <v>311</v>
+      <c r="A79" s="19" t="s">
+        <v>312</v>
       </c>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -18736,8 +18742,8 @@
       <c r="GU79" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="19.5">
-      <c r="A80" s="18" t="s">
-        <v>312</v>
+      <c r="A80" s="19" t="s">
+        <v>313</v>
       </c>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -18943,8 +18949,8 @@
       <c r="GU80" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="19.5">
-      <c r="A81" s="18" t="s">
-        <v>313</v>
+      <c r="A81" s="19" t="s">
+        <v>314</v>
       </c>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -19150,8 +19156,8 @@
       <c r="GU81" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="19.5">
-      <c r="A82" s="18" t="s">
-        <v>314</v>
+      <c r="A82" s="19" t="s">
+        <v>315</v>
       </c>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -19357,8 +19363,8 @@
       <c r="GU82" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="19.5">
-      <c r="A83" s="18" t="s">
-        <v>315</v>
+      <c r="A83" s="19" t="s">
+        <v>316</v>
       </c>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -19564,8 +19570,8 @@
       <c r="GU83" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="19.5">
-      <c r="A84" s="18" t="s">
-        <v>316</v>
+      <c r="A84" s="19" t="s">
+        <v>317</v>
       </c>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -19771,8 +19777,8 @@
       <c r="GU84" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="19.5">
-      <c r="A85" s="18" t="s">
-        <v>317</v>
+      <c r="A85" s="19" t="s">
+        <v>318</v>
       </c>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -19978,8 +19984,8 @@
       <c r="GU85" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="19.5">
-      <c r="A86" s="18" t="s">
-        <v>318</v>
+      <c r="A86" s="19" t="s">
+        <v>319</v>
       </c>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -20185,8 +20191,8 @@
       <c r="GU86" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="19.5">
-      <c r="A87" s="18" t="s">
-        <v>319</v>
+      <c r="A87" s="19" t="s">
+        <v>320</v>
       </c>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -20392,8 +20398,8 @@
       <c r="GU87" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="19.5">
-      <c r="A88" s="18" t="s">
-        <v>320</v>
+      <c r="A88" s="19" t="s">
+        <v>321</v>
       </c>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -20599,8 +20605,8 @@
       <c r="GU88" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="19.5">
-      <c r="A89" s="18" t="s">
-        <v>321</v>
+      <c r="A89" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -20806,8 +20812,8 @@
       <c r="GU89" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="19.5">
-      <c r="A90" s="18" t="s">
-        <v>322</v>
+      <c r="A90" s="19" t="s">
+        <v>323</v>
       </c>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -21013,8 +21019,8 @@
       <c r="GU90" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="19.5">
-      <c r="A91" s="18" t="s">
-        <v>323</v>
+      <c r="A91" s="19" t="s">
+        <v>324</v>
       </c>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -21220,8 +21226,8 @@
       <c r="GU91" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="19.5">
-      <c r="A92" s="18" t="s">
-        <v>324</v>
+      <c r="A92" s="19" t="s">
+        <v>325</v>
       </c>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -21427,8 +21433,8 @@
       <c r="GU92" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="19.5">
-      <c r="A93" s="18" t="s">
-        <v>325</v>
+      <c r="A93" s="19" t="s">
+        <v>326</v>
       </c>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -21634,8 +21640,8 @@
       <c r="GU93" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="19.5">
-      <c r="A94" s="18" t="s">
-        <v>326</v>
+      <c r="A94" s="19" t="s">
+        <v>327</v>
       </c>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -21841,8 +21847,8 @@
       <c r="GU94" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="19.5">
-      <c r="A95" s="18" t="s">
-        <v>327</v>
+      <c r="A95" s="19" t="s">
+        <v>328</v>
       </c>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -22048,8 +22054,8 @@
       <c r="GU95" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="19.5">
-      <c r="A96" s="18" t="s">
-        <v>328</v>
+      <c r="A96" s="19" t="s">
+        <v>329</v>
       </c>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -22255,8 +22261,8 @@
       <c r="GU96" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="19.5">
-      <c r="A97" s="18" t="s">
-        <v>329</v>
+      <c r="A97" s="19" t="s">
+        <v>330</v>
       </c>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -22462,8 +22468,8 @@
       <c r="GU97" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="19.5">
-      <c r="A98" s="18" t="s">
-        <v>330</v>
+      <c r="A98" s="19" t="s">
+        <v>331</v>
       </c>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -22669,8 +22675,8 @@
       <c r="GU98" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="19.5">
-      <c r="A99" s="18" t="s">
-        <v>331</v>
+      <c r="A99" s="19" t="s">
+        <v>332</v>
       </c>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -22876,8 +22882,8 @@
       <c r="GU99" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="19.5">
-      <c r="A100" s="18" t="s">
-        <v>332</v>
+      <c r="A100" s="19" t="s">
+        <v>333</v>
       </c>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -22959,7 +22965,7 @@
       <c r="CA100" s="3"/>
       <c r="CB100" s="3"/>
       <c r="CC100" s="3"/>
-      <c r="CD100" s="20">
+      <c r="CD100" s="21">
         <v>1</v>
       </c>
       <c r="CE100" s="3"/>
@@ -23085,8 +23091,8 @@
       <c r="GU100" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="19.5">
-      <c r="A101" s="18" t="s">
-        <v>333</v>
+      <c r="A101" s="19" t="s">
+        <v>334</v>
       </c>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -23292,8 +23298,8 @@
       <c r="GU101" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="19.5">
-      <c r="A102" s="18" t="s">
-        <v>334</v>
+      <c r="A102" s="19" t="s">
+        <v>335</v>
       </c>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -23499,8 +23505,8 @@
       <c r="GU102" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="19.5">
-      <c r="A103" s="18" t="s">
-        <v>335</v>
+      <c r="A103" s="19" t="s">
+        <v>336</v>
       </c>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -23706,8 +23712,8 @@
       <c r="GU103" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="19.5">
-      <c r="A104" s="18" t="s">
-        <v>336</v>
+      <c r="A104" s="19" t="s">
+        <v>337</v>
       </c>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -23913,8 +23919,8 @@
       <c r="GU104" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="19.5">
-      <c r="A105" s="18" t="s">
-        <v>337</v>
+      <c r="A105" s="19" t="s">
+        <v>338</v>
       </c>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -24120,8 +24126,8 @@
       <c r="GU105" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="19.5">
-      <c r="A106" s="18" t="s">
-        <v>338</v>
+      <c r="A106" s="19" t="s">
+        <v>339</v>
       </c>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -24327,8 +24333,8 @@
       <c r="GU106" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="19.5">
-      <c r="A107" s="18" t="s">
-        <v>339</v>
+      <c r="A107" s="19" t="s">
+        <v>340</v>
       </c>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -24534,8 +24540,8 @@
       <c r="GU107" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="19.5">
-      <c r="A108" s="18" t="s">
-        <v>340</v>
+      <c r="A108" s="19" t="s">
+        <v>341</v>
       </c>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -24741,8 +24747,8 @@
       <c r="GU108" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="19.5">
-      <c r="A109" s="18" t="s">
-        <v>341</v>
+      <c r="A109" s="19" t="s">
+        <v>342</v>
       </c>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -24948,8 +24954,8 @@
       <c r="GU109" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="19.5">
-      <c r="A110" s="18" t="s">
-        <v>342</v>
+      <c r="A110" s="19" t="s">
+        <v>343</v>
       </c>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -25155,8 +25161,8 @@
       <c r="GU110" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="19.5">
-      <c r="A111" s="18" t="s">
-        <v>343</v>
+      <c r="A111" s="19" t="s">
+        <v>344</v>
       </c>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -25362,8 +25368,8 @@
       <c r="GU111" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="19.5">
-      <c r="A112" s="18" t="s">
-        <v>344</v>
+      <c r="A112" s="19" t="s">
+        <v>345</v>
       </c>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -25569,8 +25575,8 @@
       <c r="GU112" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="19.5">
-      <c r="A113" s="18" t="s">
-        <v>345</v>
+      <c r="A113" s="19" t="s">
+        <v>346</v>
       </c>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -25776,8 +25782,8 @@
       <c r="GU113" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="19.5">
-      <c r="A114" s="18" t="s">
-        <v>346</v>
+      <c r="A114" s="19" t="s">
+        <v>347</v>
       </c>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -25983,8 +25989,8 @@
       <c r="GU114" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="19.5">
-      <c r="A115" s="18" t="s">
-        <v>347</v>
+      <c r="A115" s="19" t="s">
+        <v>348</v>
       </c>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -26190,8 +26196,8 @@
       <c r="GU115" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="19.5">
-      <c r="A116" s="18" t="s">
-        <v>348</v>
+      <c r="A116" s="19" t="s">
+        <v>349</v>
       </c>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -26397,8 +26403,8 @@
       <c r="GU116" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="19.5">
-      <c r="A117" s="18" t="s">
-        <v>349</v>
+      <c r="A117" s="19" t="s">
+        <v>350</v>
       </c>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -26604,8 +26610,8 @@
       <c r="GU117" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="19.5">
-      <c r="A118" s="18" t="s">
-        <v>350</v>
+      <c r="A118" s="19" t="s">
+        <v>351</v>
       </c>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -26811,8 +26817,8 @@
       <c r="GU118" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="19.5">
-      <c r="A119" s="18" t="s">
-        <v>351</v>
+      <c r="A119" s="19" t="s">
+        <v>352</v>
       </c>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -27018,8 +27024,8 @@
       <c r="GU119" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="19.5">
-      <c r="A120" s="18" t="s">
-        <v>352</v>
+      <c r="A120" s="19" t="s">
+        <v>353</v>
       </c>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
@@ -27225,8 +27231,8 @@
       <c r="GU120" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="19.5">
-      <c r="A121" s="18" t="s">
-        <v>353</v>
+      <c r="A121" s="19" t="s">
+        <v>354</v>
       </c>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -27432,8 +27438,8 @@
       <c r="GU121" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="19.5">
-      <c r="A122" s="18" t="s">
-        <v>354</v>
+      <c r="A122" s="19" t="s">
+        <v>355</v>
       </c>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
@@ -27639,8 +27645,8 @@
       <c r="GU122" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="19.5">
-      <c r="A123" s="18" t="s">
-        <v>355</v>
+      <c r="A123" s="19" t="s">
+        <v>356</v>
       </c>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -27846,8 +27852,8 @@
       <c r="GU123" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="19.5">
-      <c r="A124" s="18" t="s">
-        <v>356</v>
+      <c r="A124" s="19" t="s">
+        <v>357</v>
       </c>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
@@ -28053,8 +28059,8 @@
       <c r="GU124" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="19.5">
-      <c r="A125" s="18" t="s">
-        <v>357</v>
+      <c r="A125" s="19" t="s">
+        <v>358</v>
       </c>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -28260,8 +28266,8 @@
       <c r="GU125" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="19.5">
-      <c r="A126" s="18" t="s">
-        <v>358</v>
+      <c r="A126" s="19" t="s">
+        <v>359</v>
       </c>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
@@ -28467,8 +28473,8 @@
       <c r="GU126" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="19.5">
-      <c r="A127" s="18" t="s">
-        <v>359</v>
+      <c r="A127" s="19" t="s">
+        <v>360</v>
       </c>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -28674,8 +28680,8 @@
       <c r="GU127" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="19.5">
-      <c r="A128" s="18" t="s">
-        <v>360</v>
+      <c r="A128" s="19" t="s">
+        <v>361</v>
       </c>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -28881,8 +28887,8 @@
       <c r="GU128" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="19.5">
-      <c r="A129" s="18" t="s">
-        <v>361</v>
+      <c r="A129" s="19" t="s">
+        <v>362</v>
       </c>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -29088,8 +29094,8 @@
       <c r="GU129" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="19.5">
-      <c r="A130" s="18" t="s">
-        <v>362</v>
+      <c r="A130" s="19" t="s">
+        <v>363</v>
       </c>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
@@ -29295,8 +29301,8 @@
       <c r="GU130" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="19.5">
-      <c r="A131" s="18" t="s">
-        <v>363</v>
+      <c r="A131" s="19" t="s">
+        <v>364</v>
       </c>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -29502,8 +29508,8 @@
       <c r="GU131" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="19.5">
-      <c r="A132" s="18" t="s">
-        <v>364</v>
+      <c r="A132" s="19" t="s">
+        <v>365</v>
       </c>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
@@ -29709,8 +29715,8 @@
       <c r="GU132" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="19.5">
-      <c r="A133" s="18" t="s">
-        <v>365</v>
+      <c r="A133" s="19" t="s">
+        <v>366</v>
       </c>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -29916,8 +29922,8 @@
       <c r="GU133" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="19.5">
-      <c r="A134" s="18" t="s">
-        <v>366</v>
+      <c r="A134" s="19" t="s">
+        <v>367</v>
       </c>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
@@ -30123,8 +30129,8 @@
       <c r="GU134" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="19.5">
-      <c r="A135" s="18" t="s">
-        <v>367</v>
+      <c r="A135" s="19" t="s">
+        <v>368</v>
       </c>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
@@ -30330,8 +30336,8 @@
       <c r="GU135" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="19.5">
-      <c r="A136" s="18" t="s">
-        <v>368</v>
+      <c r="A136" s="19" t="s">
+        <v>369</v>
       </c>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
@@ -30537,8 +30543,8 @@
       <c r="GU136" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="19.5">
-      <c r="A137" s="18" t="s">
-        <v>369</v>
+      <c r="A137" s="19" t="s">
+        <v>370</v>
       </c>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -30744,8 +30750,8 @@
       <c r="GU137" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="19.5">
-      <c r="A138" s="18" t="s">
-        <v>370</v>
+      <c r="A138" s="19" t="s">
+        <v>371</v>
       </c>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
@@ -30951,8 +30957,8 @@
       <c r="GU138" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="19.5">
-      <c r="A139" s="18" t="s">
-        <v>371</v>
+      <c r="A139" s="19" t="s">
+        <v>372</v>
       </c>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
@@ -31158,8 +31164,8 @@
       <c r="GU139" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="19.5">
-      <c r="A140" s="18" t="s">
-        <v>372</v>
+      <c r="A140" s="19" t="s">
+        <v>373</v>
       </c>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
@@ -31365,8 +31371,8 @@
       <c r="GU140" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="19.5">
-      <c r="A141" s="18" t="s">
-        <v>373</v>
+      <c r="A141" s="19" t="s">
+        <v>374</v>
       </c>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
@@ -31572,8 +31578,8 @@
       <c r="GU141" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="19.5">
-      <c r="A142" s="18" t="s">
-        <v>374</v>
+      <c r="A142" s="19" t="s">
+        <v>375</v>
       </c>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
@@ -31779,8 +31785,8 @@
       <c r="GU142" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="19.5">
-      <c r="A143" s="18" t="s">
-        <v>375</v>
+      <c r="A143" s="19" t="s">
+        <v>376</v>
       </c>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
@@ -31986,8 +31992,8 @@
       <c r="GU143" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="19.5">
-      <c r="A144" s="18" t="s">
-        <v>376</v>
+      <c r="A144" s="19" t="s">
+        <v>377</v>
       </c>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
@@ -32193,8 +32199,8 @@
       <c r="GU144" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="19.5">
-      <c r="A145" s="18" t="s">
-        <v>377</v>
+      <c r="A145" s="19" t="s">
+        <v>378</v>
       </c>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
@@ -32400,8 +32406,8 @@
       <c r="GU145" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="19.5">
-      <c r="A146" s="18" t="s">
-        <v>378</v>
+      <c r="A146" s="19" t="s">
+        <v>379</v>
       </c>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
@@ -32607,8 +32613,8 @@
       <c r="GU146" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="19.5">
-      <c r="A147" s="18" t="s">
-        <v>379</v>
+      <c r="A147" s="19" t="s">
+        <v>380</v>
       </c>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
@@ -32814,8 +32820,8 @@
       <c r="GU147" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="19.5">
-      <c r="A148" s="18" t="s">
-        <v>380</v>
+      <c r="A148" s="19" t="s">
+        <v>381</v>
       </c>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
@@ -33021,8 +33027,8 @@
       <c r="GU148" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="19.5">
-      <c r="A149" s="18" t="s">
-        <v>381</v>
+      <c r="A149" s="19" t="s">
+        <v>382</v>
       </c>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
@@ -33228,8 +33234,8 @@
       <c r="GU149" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="19.5">
-      <c r="A150" s="18" t="s">
-        <v>382</v>
+      <c r="A150" s="19" t="s">
+        <v>383</v>
       </c>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
@@ -33435,8 +33441,8 @@
       <c r="GU150" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="19.5">
-      <c r="A151" s="18" t="s">
-        <v>383</v>
+      <c r="A151" s="19" t="s">
+        <v>384</v>
       </c>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
@@ -33642,8 +33648,8 @@
       <c r="GU151" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="19.5">
-      <c r="A152" s="18" t="s">
-        <v>384</v>
+      <c r="A152" s="19" t="s">
+        <v>385</v>
       </c>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
@@ -33849,8 +33855,8 @@
       <c r="GU152" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="19.5">
-      <c r="A153" s="18" t="s">
-        <v>385</v>
+      <c r="A153" s="19" t="s">
+        <v>386</v>
       </c>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
@@ -34056,8 +34062,8 @@
       <c r="GU153" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="19.5">
-      <c r="A154" s="18" t="s">
-        <v>386</v>
+      <c r="A154" s="19" t="s">
+        <v>387</v>
       </c>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
@@ -34263,8 +34269,8 @@
       <c r="GU154" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="19.5">
-      <c r="A155" s="18" t="s">
-        <v>387</v>
+      <c r="A155" s="19" t="s">
+        <v>388</v>
       </c>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
@@ -34470,8 +34476,8 @@
       <c r="GU155" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="19.5">
-      <c r="A156" s="18" t="s">
-        <v>388</v>
+      <c r="A156" s="19" t="s">
+        <v>389</v>
       </c>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
@@ -34677,8 +34683,8 @@
       <c r="GU156" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="19.5">
-      <c r="A157" s="18" t="s">
-        <v>389</v>
+      <c r="A157" s="19" t="s">
+        <v>390</v>
       </c>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
@@ -34884,8 +34890,8 @@
       <c r="GU157" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="19.5">
-      <c r="A158" s="18" t="s">
-        <v>390</v>
+      <c r="A158" s="19" t="s">
+        <v>391</v>
       </c>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
@@ -35091,8 +35097,8 @@
       <c r="GU158" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="19.5">
-      <c r="A159" s="18" t="s">
-        <v>391</v>
+      <c r="A159" s="19" t="s">
+        <v>392</v>
       </c>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
@@ -35298,8 +35304,8 @@
       <c r="GU159" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="19.5">
-      <c r="A160" s="18" t="s">
-        <v>392</v>
+      <c r="A160" s="19" t="s">
+        <v>393</v>
       </c>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
@@ -35505,8 +35511,8 @@
       <c r="GU160" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="19.5">
-      <c r="A161" s="18" t="s">
-        <v>393</v>
+      <c r="A161" s="19" t="s">
+        <v>394</v>
       </c>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
@@ -35712,8 +35718,8 @@
       <c r="GU161" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="19.5">
-      <c r="A162" s="18" t="s">
-        <v>394</v>
+      <c r="A162" s="19" t="s">
+        <v>395</v>
       </c>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
@@ -35919,8 +35925,8 @@
       <c r="GU162" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="19.5">
-      <c r="A163" s="18" t="s">
-        <v>395</v>
+      <c r="A163" s="19" t="s">
+        <v>396</v>
       </c>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
@@ -36126,8 +36132,8 @@
       <c r="GU163" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="19.5">
-      <c r="A164" s="18" t="s">
-        <v>396</v>
+      <c r="A164" s="19" t="s">
+        <v>397</v>
       </c>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
@@ -36333,8 +36339,8 @@
       <c r="GU164" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="19.5">
-      <c r="A165" s="18" t="s">
-        <v>397</v>
+      <c r="A165" s="19" t="s">
+        <v>398</v>
       </c>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
@@ -36540,8 +36546,8 @@
       <c r="GU165" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="19.5">
-      <c r="A166" s="18" t="s">
-        <v>398</v>
+      <c r="A166" s="19" t="s">
+        <v>399</v>
       </c>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
@@ -36747,8 +36753,8 @@
       <c r="GU166" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="19.5">
-      <c r="A167" s="18" t="s">
-        <v>399</v>
+      <c r="A167" s="19" t="s">
+        <v>400</v>
       </c>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
@@ -36954,8 +36960,8 @@
       <c r="GU167" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="19.5">
-      <c r="A168" s="18" t="s">
-        <v>400</v>
+      <c r="A168" s="19" t="s">
+        <v>401</v>
       </c>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
@@ -37161,8 +37167,8 @@
       <c r="GU168" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="19.5">
-      <c r="A169" s="18" t="s">
-        <v>401</v>
+      <c r="A169" s="19" t="s">
+        <v>402</v>
       </c>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
@@ -37368,8 +37374,8 @@
       <c r="GU169" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="19.5">
-      <c r="A170" s="18" t="s">
-        <v>402</v>
+      <c r="A170" s="19" t="s">
+        <v>403</v>
       </c>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
@@ -37575,8 +37581,8 @@
       <c r="GU170" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="19.5">
-      <c r="A171" s="18" t="s">
-        <v>403</v>
+      <c r="A171" s="19" t="s">
+        <v>404</v>
       </c>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
@@ -37782,8 +37788,8 @@
       <c r="GU171" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="19.5">
-      <c r="A172" s="18" t="s">
-        <v>404</v>
+      <c r="A172" s="19" t="s">
+        <v>405</v>
       </c>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
@@ -37989,8 +37995,8 @@
       <c r="GU172" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="19.5">
-      <c r="A173" s="18" t="s">
-        <v>405</v>
+      <c r="A173" s="19" t="s">
+        <v>406</v>
       </c>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
@@ -38196,8 +38202,8 @@
       <c r="GU173" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="19.5">
-      <c r="A174" s="18" t="s">
-        <v>406</v>
+      <c r="A174" s="19" t="s">
+        <v>407</v>
       </c>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
@@ -38403,8 +38409,8 @@
       <c r="GU174" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="19.5">
-      <c r="A175" s="18" t="s">
-        <v>407</v>
+      <c r="A175" s="19" t="s">
+        <v>408</v>
       </c>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
@@ -38610,8 +38616,8 @@
       <c r="GU175" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="19.5">
-      <c r="A176" s="18" t="s">
-        <v>408</v>
+      <c r="A176" s="19" t="s">
+        <v>409</v>
       </c>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
@@ -38817,8 +38823,8 @@
       <c r="GU176" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="19.5">
-      <c r="A177" s="18" t="s">
-        <v>409</v>
+      <c r="A177" s="19" t="s">
+        <v>410</v>
       </c>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
@@ -39024,8 +39030,8 @@
       <c r="GU177" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="19.5">
-      <c r="A178" s="18" t="s">
-        <v>410</v>
+      <c r="A178" s="19" t="s">
+        <v>411</v>
       </c>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
@@ -39231,8 +39237,8 @@
       <c r="GU178" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="19.5">
-      <c r="A179" s="18" t="s">
-        <v>411</v>
+      <c r="A179" s="19" t="s">
+        <v>412</v>
       </c>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
@@ -39438,8 +39444,8 @@
       <c r="GU179" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="19.5">
-      <c r="A180" s="18" t="s">
-        <v>412</v>
+      <c r="A180" s="19" t="s">
+        <v>413</v>
       </c>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
@@ -39645,8 +39651,8 @@
       <c r="GU180" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="19.5">
-      <c r="A181" s="18" t="s">
-        <v>413</v>
+      <c r="A181" s="19" t="s">
+        <v>414</v>
       </c>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
@@ -39852,8 +39858,8 @@
       <c r="GU181" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="19.5">
-      <c r="A182" s="18" t="s">
-        <v>414</v>
+      <c r="A182" s="19" t="s">
+        <v>415</v>
       </c>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
@@ -40059,8 +40065,8 @@
       <c r="GU182" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="19.5">
-      <c r="A183" s="18" t="s">
-        <v>415</v>
+      <c r="A183" s="19" t="s">
+        <v>416</v>
       </c>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
@@ -40266,8 +40272,8 @@
       <c r="GU183" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="19.5">
-      <c r="A184" s="18" t="s">
-        <v>416</v>
+      <c r="A184" s="19" t="s">
+        <v>417</v>
       </c>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
@@ -40473,8 +40479,8 @@
       <c r="GU184" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="19.5">
-      <c r="A185" s="18" t="s">
-        <v>417</v>
+      <c r="A185" s="19" t="s">
+        <v>418</v>
       </c>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
@@ -40680,8 +40686,8 @@
       <c r="GU185" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="19.5">
-      <c r="A186" s="18" t="s">
-        <v>418</v>
+      <c r="A186" s="19" t="s">
+        <v>419</v>
       </c>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
@@ -40887,8 +40893,8 @@
       <c r="GU186" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="19.5">
-      <c r="A187" s="18" t="s">
-        <v>419</v>
+      <c r="A187" s="19" t="s">
+        <v>420</v>
       </c>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
@@ -41094,8 +41100,8 @@
       <c r="GU187" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="19.5">
-      <c r="A188" s="18" t="s">
-        <v>420</v>
+      <c r="A188" s="19" t="s">
+        <v>421</v>
       </c>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
@@ -41301,8 +41307,8 @@
       <c r="GU188" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="19.5">
-      <c r="A189" s="18" t="s">
-        <v>421</v>
+      <c r="A189" s="19" t="s">
+        <v>422</v>
       </c>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
@@ -41508,8 +41514,8 @@
       <c r="GU189" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="19.5">
-      <c r="A190" s="18" t="s">
-        <v>422</v>
+      <c r="A190" s="19" t="s">
+        <v>423</v>
       </c>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
@@ -41715,8 +41721,8 @@
       <c r="GU190" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="19.5">
-      <c r="A191" s="18" t="s">
-        <v>423</v>
+      <c r="A191" s="19" t="s">
+        <v>424</v>
       </c>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
@@ -41922,8 +41928,8 @@
       <c r="GU191" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="19.5">
-      <c r="A192" s="18" t="s">
-        <v>424</v>
+      <c r="A192" s="19" t="s">
+        <v>425</v>
       </c>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
@@ -42129,8 +42135,8 @@
       <c r="GU192" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="19.5">
-      <c r="A193" s="18" t="s">
-        <v>425</v>
+      <c r="A193" s="19" t="s">
+        <v>426</v>
       </c>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
@@ -42336,8 +42342,8 @@
       <c r="GU193" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="19.5">
-      <c r="A194" s="18" t="s">
-        <v>426</v>
+      <c r="A194" s="19" t="s">
+        <v>427</v>
       </c>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
@@ -42543,8 +42549,8 @@
       <c r="GU194" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="19.5">
-      <c r="A195" s="18" t="s">
-        <v>427</v>
+      <c r="A195" s="19" t="s">
+        <v>428</v>
       </c>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
@@ -42750,8 +42756,8 @@
       <c r="GU195" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="19.5">
-      <c r="A196" s="18" t="s">
-        <v>428</v>
+      <c r="A196" s="19" t="s">
+        <v>429</v>
       </c>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
@@ -42957,8 +42963,8 @@
       <c r="GU196" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="19.5">
-      <c r="A197" s="18" t="s">
-        <v>429</v>
+      <c r="A197" s="19" t="s">
+        <v>430</v>
       </c>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
@@ -43164,8 +43170,8 @@
       <c r="GU197" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="19.5">
-      <c r="A198" s="18" t="s">
-        <v>430</v>
+      <c r="A198" s="19" t="s">
+        <v>431</v>
       </c>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
@@ -43371,8 +43377,8 @@
       <c r="GU198" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="19.5">
-      <c r="A199" s="18" t="s">
-        <v>431</v>
+      <c r="A199" s="19" t="s">
+        <v>432</v>
       </c>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
@@ -43578,8 +43584,8 @@
       <c r="GU199" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="19.5">
-      <c r="A200" s="18" t="s">
-        <v>432</v>
+      <c r="A200" s="19" t="s">
+        <v>433</v>
       </c>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
@@ -43785,8 +43791,8 @@
       <c r="GU200" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="201" customHeight="1" ht="19.5">
-      <c r="A201" s="18" t="s">
-        <v>433</v>
+      <c r="A201" s="19" t="s">
+        <v>434</v>
       </c>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
@@ -43992,8 +43998,8 @@
       <c r="GU201" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="202" customHeight="1" ht="19.5">
-      <c r="A202" s="18" t="s">
-        <v>434</v>
+      <c r="A202" s="19" t="s">
+        <v>435</v>
       </c>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
@@ -44199,7 +44205,7 @@
       <c r="GU202" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="203" customHeight="1" ht="19.5">
-      <c r="A203" s="18"/>
+      <c r="A203" s="19"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
       <c r="D203" s="3"/>
@@ -44404,7 +44410,7 @@
       <c r="GU203" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="204" customHeight="1" ht="19.5">
-      <c r="A204" s="18"/>
+      <c r="A204" s="19"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
@@ -44609,7 +44615,7 @@
       <c r="GU204" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="205" customHeight="1" ht="19.5">
-      <c r="A205" s="18"/>
+      <c r="A205" s="19"/>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
@@ -44814,7 +44820,7 @@
       <c r="GU205" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="206" customHeight="1" ht="19.5">
-      <c r="A206" s="18"/>
+      <c r="A206" s="19"/>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
@@ -45019,7 +45025,7 @@
       <c r="GU206" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="207" customHeight="1" ht="19.5">
-      <c r="A207" s="18"/>
+      <c r="A207" s="19"/>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
@@ -45224,7 +45230,7 @@
       <c r="GU207" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="208" customHeight="1" ht="19.5">
-      <c r="A208" s="18"/>
+      <c r="A208" s="19"/>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
@@ -45429,7 +45435,7 @@
       <c r="GU208" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="209" customHeight="1" ht="19.5">
-      <c r="A209" s="18"/>
+      <c r="A209" s="19"/>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
@@ -45634,7 +45640,7 @@
       <c r="GU209" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="210" customHeight="1" ht="19.5">
-      <c r="A210" s="18"/>
+      <c r="A210" s="19"/>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
@@ -45839,7 +45845,7 @@
       <c r="GU210" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="211" customHeight="1" ht="19.5">
-      <c r="A211" s="18"/>
+      <c r="A211" s="19"/>
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
@@ -46044,7 +46050,7 @@
       <c r="GU211" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="212" customHeight="1" ht="19.5">
-      <c r="A212" s="18"/>
+      <c r="A212" s="19"/>
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
       <c r="D212" s="3"/>
@@ -46249,7 +46255,7 @@
       <c r="GU212" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="213" customHeight="1" ht="19.5">
-      <c r="A213" s="18"/>
+      <c r="A213" s="19"/>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
       <c r="D213" s="3"/>
@@ -46454,7 +46460,7 @@
       <c r="GU213" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="214" customHeight="1" ht="19.5">
-      <c r="A214" s="18"/>
+      <c r="A214" s="19"/>
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
@@ -46659,7 +46665,7 @@
       <c r="GU214" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="215" customHeight="1" ht="19.5">
-      <c r="A215" s="18"/>
+      <c r="A215" s="19"/>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
@@ -46864,7 +46870,7 @@
       <c r="GU215" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="216" customHeight="1" ht="19.5">
-      <c r="A216" s="18"/>
+      <c r="A216" s="19"/>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
       <c r="D216" s="3"/>
@@ -47069,7 +47075,7 @@
       <c r="GU216" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="217" customHeight="1" ht="19.5">
-      <c r="A217" s="18"/>
+      <c r="A217" s="19"/>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
@@ -47274,7 +47280,7 @@
       <c r="GU217" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="218" customHeight="1" ht="19.5">
-      <c r="A218" s="18"/>
+      <c r="A218" s="19"/>
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
       <c r="D218" s="3"/>
@@ -47479,7 +47485,7 @@
       <c r="GU218" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="219" customHeight="1" ht="19.5">
-      <c r="A219" s="18"/>
+      <c r="A219" s="19"/>
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
       <c r="D219" s="3"/>
@@ -47684,7 +47690,7 @@
       <c r="GU219" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="220" customHeight="1" ht="19.5">
-      <c r="A220" s="18"/>
+      <c r="A220" s="19"/>
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
       <c r="D220" s="3"/>
@@ -47889,7 +47895,7 @@
       <c r="GU220" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="221" customHeight="1" ht="19.5">
-      <c r="A221" s="18"/>
+      <c r="A221" s="19"/>
       <c r="B221" s="3"/>
       <c r="C221" s="3"/>
       <c r="D221" s="3"/>
@@ -48094,7 +48100,7 @@
       <c r="GU221" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="222" customHeight="1" ht="19.5">
-      <c r="A222" s="18"/>
+      <c r="A222" s="19"/>
       <c r="B222" s="3"/>
       <c r="C222" s="3"/>
       <c r="D222" s="3"/>
@@ -48299,7 +48305,7 @@
       <c r="GU222" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="223" customHeight="1" ht="19.5">
-      <c r="A223" s="18"/>
+      <c r="A223" s="19"/>
       <c r="B223" s="3"/>
       <c r="C223" s="3"/>
       <c r="D223" s="3"/>
@@ -48504,7 +48510,7 @@
       <c r="GU223" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="224" customHeight="1" ht="19.5">
-      <c r="A224" s="18"/>
+      <c r="A224" s="19"/>
       <c r="B224" s="3"/>
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
@@ -48709,7 +48715,7 @@
       <c r="GU224" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="225" customHeight="1" ht="19.5">
-      <c r="A225" s="18"/>
+      <c r="A225" s="19"/>
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
       <c r="D225" s="3"/>
@@ -48914,7 +48920,7 @@
       <c r="GU225" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="226" customHeight="1" ht="19.5">
-      <c r="A226" s="18"/>
+      <c r="A226" s="19"/>
       <c r="B226" s="3"/>
       <c r="C226" s="3"/>
       <c r="D226" s="3"/>
@@ -49119,7 +49125,7 @@
       <c r="GU226" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="227" customHeight="1" ht="19.5">
-      <c r="A227" s="18"/>
+      <c r="A227" s="19"/>
       <c r="B227" s="3"/>
       <c r="C227" s="3"/>
       <c r="D227" s="3"/>
@@ -49324,7 +49330,7 @@
       <c r="GU227" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="228" customHeight="1" ht="19.5">
-      <c r="A228" s="18"/>
+      <c r="A228" s="19"/>
       <c r="B228" s="3"/>
       <c r="C228" s="3"/>
       <c r="D228" s="3"/>
@@ -49529,7 +49535,7 @@
       <c r="GU228" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="229" customHeight="1" ht="19.5">
-      <c r="A229" s="18"/>
+      <c r="A229" s="19"/>
       <c r="B229" s="3"/>
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
@@ -49734,7 +49740,7 @@
       <c r="GU229" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="230" customHeight="1" ht="19.5">
-      <c r="A230" s="18"/>
+      <c r="A230" s="19"/>
       <c r="B230" s="3"/>
       <c r="C230" s="3"/>
       <c r="D230" s="3"/>
@@ -49939,7 +49945,7 @@
       <c r="GU230" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="231" customHeight="1" ht="19.5">
-      <c r="A231" s="18"/>
+      <c r="A231" s="19"/>
       <c r="B231" s="3"/>
       <c r="C231" s="3"/>
       <c r="D231" s="3"/>
@@ -50144,7 +50150,7 @@
       <c r="GU231" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="232" customHeight="1" ht="19.5">
-      <c r="A232" s="18"/>
+      <c r="A232" s="19"/>
       <c r="B232" s="3"/>
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
@@ -50349,7 +50355,7 @@
       <c r="GU232" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="233" customHeight="1" ht="19.5">
-      <c r="A233" s="18"/>
+      <c r="A233" s="19"/>
       <c r="B233" s="3"/>
       <c r="C233" s="3"/>
       <c r="D233" s="3"/>
@@ -50554,7 +50560,7 @@
       <c r="GU233" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="234" customHeight="1" ht="19.5">
-      <c r="A234" s="18"/>
+      <c r="A234" s="19"/>
       <c r="B234" s="3"/>
       <c r="C234" s="3"/>
       <c r="D234" s="3"/>
@@ -50759,7 +50765,7 @@
       <c r="GU234" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="235" customHeight="1" ht="19.5">
-      <c r="A235" s="18"/>
+      <c r="A235" s="19"/>
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
       <c r="D235" s="3"/>
@@ -50964,7 +50970,7 @@
       <c r="GU235" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="236" customHeight="1" ht="19.5">
-      <c r="A236" s="18"/>
+      <c r="A236" s="19"/>
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
       <c r="D236" s="3"/>
@@ -51169,7 +51175,7 @@
       <c r="GU236" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="237" customHeight="1" ht="19.5">
-      <c r="A237" s="18"/>
+      <c r="A237" s="19"/>
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
       <c r="D237" s="3"/>
@@ -51374,7 +51380,7 @@
       <c r="GU237" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="238" customHeight="1" ht="19.5">
-      <c r="A238" s="18"/>
+      <c r="A238" s="19"/>
       <c r="B238" s="3"/>
       <c r="C238" s="3"/>
       <c r="D238" s="3"/>
@@ -51579,7 +51585,7 @@
       <c r="GU238" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="239" customHeight="1" ht="19.5">
-      <c r="A239" s="18"/>
+      <c r="A239" s="19"/>
       <c r="B239" s="3"/>
       <c r="C239" s="3"/>
       <c r="D239" s="3"/>
@@ -51784,7 +51790,7 @@
       <c r="GU239" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="240" customHeight="1" ht="19.5">
-      <c r="A240" s="18"/>
+      <c r="A240" s="19"/>
       <c r="B240" s="3"/>
       <c r="C240" s="3"/>
       <c r="D240" s="3"/>
@@ -51989,7 +51995,7 @@
       <c r="GU240" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="241" customHeight="1" ht="19.5">
-      <c r="A241" s="18"/>
+      <c r="A241" s="19"/>
       <c r="B241" s="3"/>
       <c r="C241" s="3"/>
       <c r="D241" s="3"/>
@@ -52194,7 +52200,7 @@
       <c r="GU241" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="242" customHeight="1" ht="19.5">
-      <c r="A242" s="18"/>
+      <c r="A242" s="19"/>
       <c r="B242" s="3"/>
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
@@ -52399,7 +52405,7 @@
       <c r="GU242" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="243" customHeight="1" ht="19.5">
-      <c r="A243" s="18"/>
+      <c r="A243" s="19"/>
       <c r="B243" s="3"/>
       <c r="C243" s="3"/>
       <c r="D243" s="3"/>
@@ -52604,7 +52610,7 @@
       <c r="GU243" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="244" customHeight="1" ht="19.5">
-      <c r="A244" s="18"/>
+      <c r="A244" s="19"/>
       <c r="B244" s="3"/>
       <c r="C244" s="3"/>
       <c r="D244" s="3"/>
@@ -52809,7 +52815,7 @@
       <c r="GU244" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="245" customHeight="1" ht="19.5">
-      <c r="A245" s="18"/>
+      <c r="A245" s="19"/>
       <c r="B245" s="3"/>
       <c r="C245" s="3"/>
       <c r="D245" s="3"/>
@@ -53014,7 +53020,7 @@
       <c r="GU245" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="246" customHeight="1" ht="19.5">
-      <c r="A246" s="18"/>
+      <c r="A246" s="19"/>
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
       <c r="D246" s="3"/>
@@ -53219,7 +53225,7 @@
       <c r="GU246" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="247" customHeight="1" ht="19.5">
-      <c r="A247" s="18"/>
+      <c r="A247" s="19"/>
       <c r="B247" s="3"/>
       <c r="C247" s="3"/>
       <c r="D247" s="3"/>
@@ -53424,7 +53430,7 @@
       <c r="GU247" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="248" customHeight="1" ht="19.5">
-      <c r="A248" s="18"/>
+      <c r="A248" s="19"/>
       <c r="B248" s="3"/>
       <c r="C248" s="3"/>
       <c r="D248" s="3"/>
@@ -53629,7 +53635,7 @@
       <c r="GU248" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="249" customHeight="1" ht="19.5">
-      <c r="A249" s="18"/>
+      <c r="A249" s="19"/>
       <c r="B249" s="3"/>
       <c r="C249" s="3"/>
       <c r="D249" s="3"/>
@@ -53846,24 +53852,24 @@
   <dimension ref="A1:R11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="16" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="16" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="16" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="16" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="16" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="16" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="16" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="16" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="16" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="16" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="16" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="18" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="18" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="18" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="18" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="18" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="18" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="17" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="18" width="14.147857142857141" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
@@ -53945,10 +53951,10 @@
         <v>12</v>
       </c>
       <c r="L2" s="9">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="M2" s="9">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="N2" s="10"/>
       <c r="O2" s="3"/>
@@ -54252,7 +54258,9 @@
       <c r="I11" s="1"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="L11" s="12"/>
+      <c r="L11" s="16" t="s">
+        <v>33</v>
+      </c>
       <c r="M11" s="12"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
